--- a/templates/class-register.xlsx
+++ b/templates/class-register.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Register" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Register'!$A$1:$AJ$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Register'!$A$1:$AP$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Register'!$7:$8</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -655,18 +655,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AP12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" customWidth="1"/>
     <col min="2" max="2" width="23.109375" customWidth="1"/>
     <col min="3" max="3" width="37.44140625" customWidth="1"/>
-    <col min="4" max="33" width="2.5546875" customWidth="1"/>
-    <col min="34" max="35" width="8.88671875" customWidth="1"/>
-    <col min="36" max="36" width="13" customWidth="1"/>
+    <col min="4" max="39" width="2.5546875" customWidth="1"/>
+    <col min="40" max="41" width="8.88671875" customWidth="1"/>
+    <col min="42" max="42" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="23" t="s">
@@ -705,8 +705,14 @@
       <c r="AH1" s="23"/>
       <c r="AI1" s="23"/>
       <c r="AJ1" s="23"/>
+      <c r="AK1" s="23"/>
+      <c r="AL1" s="23"/>
+      <c r="AM1" s="23"/>
+      <c r="AN1" s="23"/>
+      <c r="AO1" s="23"/>
+      <c r="AP1" s="23"/>
     </row>
-    <row r="2" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="14" t="s">
@@ -749,8 +755,14 @@
       <c r="AH2" s="18"/>
       <c r="AI2" s="18"/>
       <c r="AJ2" s="18"/>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="18"/>
+      <c r="AN2" s="18"/>
+      <c r="AO2" s="18"/>
+      <c r="AP2" s="18"/>
     </row>
-    <row r="3" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="s">
@@ -793,8 +805,14 @@
       <c r="AH3" s="19"/>
       <c r="AI3" s="19"/>
       <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="19"/>
     </row>
-    <row r="4" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="s">
@@ -833,8 +851,14 @@
       <c r="AH4" s="20"/>
       <c r="AI4" s="20"/>
       <c r="AJ4" s="20"/>
+      <c r="AK4" s="20"/>
+      <c r="AL4" s="20"/>
+      <c r="AM4" s="20"/>
+      <c r="AN4" s="20"/>
+      <c r="AO4" s="20"/>
+      <c r="AP4" s="20"/>
     </row>
-    <row r="5" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -873,8 +897,14 @@
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="5"/>
+      <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
     </row>
-    <row r="6" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -913,8 +943,14 @@
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="5"/>
     </row>
-    <row r="7" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -968,17 +1004,23 @@
       </c>
       <c r="AF7" s="7"/>
       <c r="AG7" s="7"/>
-      <c r="AH7" s="21" t="s">
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="7"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="AI7" s="21" t="s">
+      <c r="AO7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="AJ7" s="21" t="s">
+      <c r="AP7" s="21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
@@ -1018,11 +1060,17 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="7"/>
-      <c r="AH8" s="21"/>
-      <c r="AI8" s="21"/>
-      <c r="AJ8" s="21"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="21"/>
+      <c r="AO8" s="21"/>
+      <c r="AP8" s="21"/>
     </row>
-    <row r="9" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1058,12 +1106,18 @@
       <c r="AG9" s="10"/>
       <c r="AH9" s="10"/>
       <c r="AI9" s="10"/>
-      <c r="AJ9" s="12" t="str">
+      <c r="AJ9" s="10"/>
+      <c r="AK9" s="10"/>
+      <c r="AL9" s="10"/>
+      <c r="AM9" s="10"/>
+      <c r="AN9" s="10"/>
+      <c r="AO9" s="10"/>
+      <c r="AP9" s="12" t="str">
         <f>IF(N(AH9)=0,"-",AI9/AH9)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1099,12 +1153,18 @@
       <c r="AG10" s="2"/>
       <c r="AH10" s="2"/>
       <c r="AI10" s="2"/>
-      <c r="AJ10" s="4" t="str">
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="2"/>
+      <c r="AL10" s="2"/>
+      <c r="AM10" s="2"/>
+      <c r="AN10" s="2"/>
+      <c r="AO10" s="2"/>
+      <c r="AP10" s="4" t="str">
         <f>IF(N(AH90)=0,"-",AI90/AH90)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
@@ -1143,8 +1203,14 @@
       <c r="AH11" s="9"/>
       <c r="AI11" s="9"/>
       <c r="AJ11" s="9"/>
+      <c r="AK11" s="9"/>
+      <c r="AL11" s="9"/>
+      <c r="AM11" s="9"/>
+      <c r="AN11" s="9"/>
+      <c r="AO11" s="9"/>
+      <c r="AP11" s="9"/>
     </row>
-    <row r="12" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>18</v>
       </c>
@@ -1183,36 +1249,44 @@
       <c r="AH12" s="9"/>
       <c r="AI12" s="9"/>
       <c r="AJ12" s="9"/>
+      <c r="AK12" s="9"/>
+      <c r="AL12" s="9"/>
+      <c r="AM12" s="9"/>
+      <c r="AN12" s="9"/>
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="AB2:AJ2"/>
-    <mergeCell ref="AB3:AJ3"/>
+  <mergeCells count="29">
+    <mergeCell ref="AB2:AP2"/>
+    <mergeCell ref="AB3:AP3"/>
     <mergeCell ref="G7:I8"/>
     <mergeCell ref="J7:L8"/>
     <mergeCell ref="M7:O8"/>
     <mergeCell ref="P7:R8"/>
     <mergeCell ref="S7:U8"/>
     <mergeCell ref="V7:X8"/>
-    <mergeCell ref="C1:AJ1"/>
+    <mergeCell ref="C1:AP1"/>
     <mergeCell ref="D2:U2"/>
-    <mergeCell ref="D4:AJ4"/>
+    <mergeCell ref="D4:AP4"/>
     <mergeCell ref="D7:F8"/>
     <mergeCell ref="Y7:AA8"/>
     <mergeCell ref="AB7:AD8"/>
     <mergeCell ref="D3:U3"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AI7:AI8"/>
-    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AP7:AP8"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D11:AJ11"/>
-    <mergeCell ref="D12:AJ12"/>
+    <mergeCell ref="D11:AP11"/>
+    <mergeCell ref="D12:AP12"/>
     <mergeCell ref="AE7:AG8"/>
-    <mergeCell ref="A5:AJ5"/>
-    <mergeCell ref="A6:AJ6"/>
+    <mergeCell ref="A5:AP5"/>
+    <mergeCell ref="A6:AP6"/>
     <mergeCell ref="V2:AA2"/>
     <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AH7:AJ8"/>
+    <mergeCell ref="AK7:AM8"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
